--- a/Data/EXCEL/Transfer/salemon/202412/6289-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/6289-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D977F2B-8D92-4E85-9DE5-8078E37520A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1043F730-D1D0-427E-89AE-0A3E41F24032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{F8B0B52D-1396-425C-9B1E-33EE971E23AE}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{58D5505D-3BAC-4D72-9215-70BCB0D964EB}"/>
   </bookViews>
   <sheets>
     <sheet name="6289-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1258,25 +1258,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0719134B-2ADA-41DB-9767-D5291F6A90BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5385121-1E78-4722-90BC-A00C6119C2B6}">
   <dimension ref="A1:Q26"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" customWidth="1"/>
-    <col min="2" max="7" width="13.6328125" customWidth="1"/>
-    <col min="8" max="8" width="16.54296875" customWidth="1"/>
-    <col min="9" max="9" width="14.36328125" customWidth="1"/>
-    <col min="10" max="10" width="13.6328125" customWidth="1"/>
-    <col min="11" max="11" width="16.54296875" customWidth="1"/>
-    <col min="12" max="12" width="13.6328125" customWidth="1"/>
-    <col min="13" max="13" width="16.54296875" customWidth="1"/>
-    <col min="14" max="14" width="14.36328125" customWidth="1"/>
-    <col min="15" max="15" width="13.6328125" customWidth="1"/>
-    <col min="16" max="16" width="16.54296875" customWidth="1"/>
-    <col min="17" max="17" width="14.81640625" customWidth="1"/>
+    <col min="1" max="1" width="11.125" customWidth="1"/>
+    <col min="2" max="7" width="8.875" customWidth="1"/>
+    <col min="8" max="8" width="10.75" customWidth="1"/>
+    <col min="9" max="9" width="9.375" customWidth="1"/>
+    <col min="10" max="10" width="8.875" customWidth="1"/>
+    <col min="11" max="11" width="10.75" customWidth="1"/>
+    <col min="12" max="12" width="8.875" customWidth="1"/>
+    <col min="13" max="13" width="10.75" customWidth="1"/>
+    <col min="14" max="14" width="9.375" customWidth="1"/>
+    <col min="15" max="15" width="8.875" customWidth="1"/>
+    <col min="16" max="16" width="10.75" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1303,7 +1303,7 @@
       <c r="P1" s="20"/>
       <c r="Q1" s="21"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="16" t="s">
         <v>4</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="Q2" s="21"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -1385,7 +1385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1424,7 +1424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>45078</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>-44.8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>45047</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>-41.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>45017</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>-45.6</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>44986</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>-49.6</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>44958</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>-36.1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>44927</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>44896</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>-48.2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>44866</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>-46.2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>44835</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>-44.8</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>44805</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>-46.8</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>44774</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>-49.1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>44743</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>-48</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>44713</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>-48.3</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>44682</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>44652</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>-46.2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>44621</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>-43.8</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>44593</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>-51.7</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>44562</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>-68.599999999999994</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>44531</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>-20.2</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>44501</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>-19.399999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>44470</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>-13.9</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>44440</v>
       </c>
